--- a/diseases/d058/2020-2025.xlsx
+++ b/diseases/d058/2020-2025.xlsx
@@ -769,11 +769,11 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0041371396062046</v>
+        <v>0.004178115174347789</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -2098,11 +2098,11 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.002874961421260823</v>
+        <v>0.002903435968614565</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -3279,11 +3279,11 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.002033509297964972</v>
+        <v>0.002053649831459083</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -4460,11 +4460,11 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.004417623647303217</v>
+        <v>0.004461377220066283</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -5641,11 +5641,11 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0.004698107688401834</v>
+        <v>0.004744639265784777</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -6970,11 +6970,11 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.007923674161035928</v>
+        <v>0.00800215279154746</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -8151,11 +8151,11 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0.008905368304881088</v>
+        <v>0.00899356995156219</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -9480,11 +9480,11 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.009676699417902284</v>
+        <v>0.009772540577288049</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -10661,11 +10661,11 @@
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>0.01290226589053638</v>
+        <v>0.01303005410305073</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -11842,11 +11842,11 @@
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.01346323397273361</v>
+        <v>0.01359657819448772</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -13171,11 +13171,11 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0.009185852345979705</v>
+        <v>0.009276831997280684</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -14352,11 +14352,11 @@
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.003856655565105983</v>
+        <v>0.003894853128629294</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -15533,11 +15533,11 @@
         <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>0.003154712866878568</v>
+        <v>0.003185615177686536</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -16862,11 +16862,11 @@
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>0.002593875023877934</v>
+        <v>0.002619283590542263</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -18043,11 +18043,11 @@
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0.002453665563127775</v>
+        <v>0.002477700693756194</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -19224,11 +19224,11 @@
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.007360996689383327</v>
+        <v>0.007433102081268583</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -20553,11 +20553,11 @@
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0.007781625071633802</v>
+        <v>0.007857850771626786</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -21734,11 +21734,11 @@
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0.007851729802008881</v>
+        <v>0.007928642220019821</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -22915,11 +22915,11 @@
         <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.007080577767883009</v>
+        <v>0.007149936287696446</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -24244,11 +24244,11 @@
         <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>0.01002497644363634</v>
+        <v>0.01012317712020388</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -25425,11 +25425,11 @@
         <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>0.01479209810914173</v>
+        <v>0.0149369956109302</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -26606,11 +26606,11 @@
         <v>0</v>
       </c>
       <c r="R177" t="n">
-        <v>0.01331989877126507</v>
+        <v>0.01345037519467648</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -27935,11 +27935,11 @@
         <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>0.01086623320813729</v>
+        <v>0.01097267450092029</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -29116,11 +29116,11 @@
         <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.006379530464132216</v>
+        <v>0.006442021803766104</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -30445,11 +30445,11 @@
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>0.004420495590194641</v>
+        <v>0.004462546484859217</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -31626,11 +31626,11 @@
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>0.002666330673450736</v>
+        <v>0.002691694705153179</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -32807,11 +32807,11 @@
         <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>0.002525997480111224</v>
+        <v>0.002550026562776695</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -33988,11 +33988,11 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>0.006244827103608303</v>
+        <v>0.006304232335753497</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -35317,11 +35317,11 @@
         <v>0</v>
       </c>
       <c r="R236" t="n">
-        <v>0.01010398992044489</v>
+        <v>0.01020010625110678</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -36498,11 +36498,11 @@
         <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0.008700657987049771</v>
+        <v>0.008783424827341952</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
@@ -37679,11 +37679,11 @@
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.01255982080388636</v>
+        <v>0.01267929874269524</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
@@ -39008,11 +39008,11 @@
         <v>0</v>
       </c>
       <c r="R261" t="n">
-        <v>0.01438415231730003</v>
+        <v>0.01452098459358952</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
@@ -40189,11 +40189,11 @@
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0.01220898782053758</v>
+        <v>0.01232512838675403</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO269" t="inlineStr">
@@ -41518,11 +41518,11 @@
         <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>0.008279658407031234</v>
+        <v>0.008358420400212502</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -42699,11 +42699,11 @@
         <v>0</v>
       </c>
       <c r="R286" t="n">
-        <v>0.00813932521369172</v>
+        <v>0.008216752257836019</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
@@ -43880,11 +43880,11 @@
         <v>0</v>
       </c>
       <c r="R294" t="n">
-        <v>0.002525997480111224</v>
+        <v>0.002550026562776695</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -45209,11 +45209,11 @@
         <v>0</v>
       </c>
       <c r="R303" t="n">
-        <v>0.002319720900038424</v>
+        <v>0.002340973419310903</v>
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO303" t="inlineStr">
@@ -46390,11 +46390,11 @@
         <v>0</v>
       </c>
       <c r="R311" t="n">
-        <v>0.003514728636421854</v>
+        <v>0.003546929423198337</v>
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO311" t="inlineStr">
@@ -47423,11 +47423,11 @@
         <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>0.005412682100089655</v>
+        <v>0.005462271311725439</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO318" t="inlineStr">
@@ -48752,11 +48752,11 @@
         <v>0</v>
       </c>
       <c r="R327" t="n">
-        <v>0.008365054154684012</v>
+        <v>0.008441692027212042</v>
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO327" t="inlineStr">
@@ -49933,11 +49933,11 @@
         <v>0</v>
       </c>
       <c r="R335" t="n">
-        <v>0.01202037193656274</v>
+        <v>0.01213049862733831</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO335" t="inlineStr">
@@ -51114,11 +51114,11 @@
         <v>0</v>
       </c>
       <c r="R343" t="n">
-        <v>0.009208589027425258</v>
+        <v>0.009292955088779644</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO343" t="inlineStr">
@@ -52443,11 +52443,11 @@
         <v>0</v>
       </c>
       <c r="R352" t="n">
-        <v>0.01187978279110587</v>
+        <v>0.01198862145041038</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO352" t="inlineStr">
@@ -53624,11 +53624,11 @@
         <v>0</v>
       </c>
       <c r="R360" t="n">
-        <v>0.01525392228207085</v>
+        <v>0.01539367369668078</v>
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO360" t="inlineStr">
@@ -54805,11 +54805,11 @@
         <v>0</v>
       </c>
       <c r="R368" t="n">
-        <v>0.01595686800935522</v>
+        <v>0.01610305958132045</v>
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO368" t="inlineStr">
@@ -56134,11 +56134,11 @@
         <v>0</v>
       </c>
       <c r="R377" t="n">
-        <v>0.01511333313661397</v>
+        <v>0.01525179651975285</v>
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO377" t="inlineStr">
